--- a/docs/verification/files/rocscience/vp106c_fem_fix.xlsx
+++ b/docs/verification/files/rocscience/vp106c_fem_fix.xlsx
@@ -1288,7 +1288,7 @@
           <t>Time:</t>
         </is>
       </c>
-      <c r="D9" s="52"/>
+      <c r="D9" s="52" t="n"/>
       <c r="F9" s="52" t="inlineStr">
         <is>
           <t>profile</t>
@@ -1306,7 +1306,7 @@
           <t xml:space="preserve">Unit weight of water: </t>
         </is>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="52" t="n">
         <v>9.81</v>
       </c>
       <c r="F10" s="52" t="inlineStr">
@@ -1327,8 +1327,8 @@
           <t>Tension crack depth:</t>
         </is>
       </c>
-      <c r="D11" s="52">
-        <v>0.0</v>
+      <c r="D11" s="52" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="52" t="inlineStr">
         <is>
@@ -1347,8 +1347,8 @@
           <t>Depth of water in crack:</t>
         </is>
       </c>
-      <c r="D12" s="52">
-        <v>0.0</v>
+      <c r="D12" s="52" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="52" t="inlineStr">
         <is>
@@ -1367,8 +1367,8 @@
           <t xml:space="preserve">Seismic coefficient (k): </t>
         </is>
       </c>
-      <c r="D13" s="52">
-        <v>0.0</v>
+      <c r="D13" s="52" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="52" t="inlineStr">
         <is>
@@ -1397,7 +1397,6 @@
           <t>Distributed loads</t>
         </is>
       </c>
-      <c r="D14"/>
     </row>
     <row r="15">
       <c r="C15" s="14" t="inlineStr">
@@ -1415,7 +1414,6 @@
           <t>Distributed loads for stage 2 of multistage analysis</t>
         </is>
       </c>
-      <c r="D15"/>
     </row>
     <row r="16">
       <c r="C16" s="14" t="inlineStr">
@@ -1433,7 +1431,6 @@
           <t>Reinforcement lines</t>
         </is>
       </c>
-      <c r="D16"/>
     </row>
     <row r="17">
       <c r="B17" s="52" t="n"/>
@@ -1442,7 +1439,7 @@
           <t>Tension SRF (FEM):</t>
         </is>
       </c>
-      <c r="D17" s="52"/>
+      <c r="D17" s="52" t="n"/>
       <c r="F17" s="52" t="inlineStr">
         <is>
           <t>piles</t>
@@ -1470,7 +1467,6 @@
           <t>Line loads</t>
         </is>
       </c>
-      <c r="D18"/>
     </row>
     <row r="19">
       <c r="C19" s="14" t="inlineStr">
@@ -1488,7 +1484,6 @@
           <t>Seepage boundary conditions</t>
         </is>
       </c>
-      <c r="D19"/>
     </row>
     <row r="20">
       <c r="C20" s="14" t="inlineStr">
@@ -1506,7 +1501,6 @@
           <t>Seepage boundary conditions for stage 2 of multistage analysis</t>
         </is>
       </c>
-      <c r="D20"/>
     </row>
     <row r="21">
       <c r="C21" s="14" t="inlineStr">
@@ -1524,7 +1518,6 @@
           <t>Transient seepage boundary conditions and run options</t>
         </is>
       </c>
-      <c r="D21"/>
     </row>
     <row r="22">
       <c r="C22" s="14" t="inlineStr">
@@ -1532,7 +1525,7 @@
           <t>Side BC:</t>
         </is>
       </c>
-      <c r="D22" s="52"/>
+      <c r="D22" s="52" t="n"/>
       <c r="F22" s="52" t="n"/>
     </row>
     <row r="23">
@@ -1555,7 +1548,7 @@
           <t>Surface family:</t>
         </is>
       </c>
-      <c r="D24" s="52"/>
+      <c r="D24" s="52" t="n"/>
     </row>
     <row r="49">
       <c r="D49" s="52" t="inlineStr">
@@ -2592,7 +2585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AA18"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="4.83203125" customWidth="1" style="52" min="1" max="1"/>
@@ -2603,6 +2596,7 @@
     <col width="5.5" customWidth="1" style="54" min="18" max="18"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
@@ -2701,7 +2695,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3">
+      <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2709,17 +2703,17 @@
           <t>pile row D1=3D (fixed head)</t>
         </is>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="D3" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="D3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="F3" s="3">
-        <v>-10.0</v>
+      <c r="F3" s="3" t="n">
+        <v>-10</v>
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
@@ -2728,22 +2722,22 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3">
-        <v>60000000.0</v>
+      <c r="N3" s="3" t="n">
+        <v>60000000</v>
       </c>
       <c r="O3" s="3" t="n"/>
       <c r="P3" s="3" t="n"/>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>unrotated</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -2946,6 +2940,7 @@
       <c r="P12" s="3" t="n"/>
       <c r="Q12" s="3" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="J14" s="9" t="n"/>
       <c r="K14" s="9" t="n"/>
@@ -5572,7 +5567,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3">
+      <c r="A11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5580,40 +5575,40 @@
           <t>Soil</t>
         </is>
       </c>
-      <c r="C11" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="D11" s="3">
-        <v>20.0</v>
+      <c r="C11" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
           <t>mc</t>
         </is>
       </c>
-      <c r="F11" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="G11" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="3">
-        <v>0.0</v>
+      <c r="F11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3">
-        <v>200000.0</v>
-      </c>
-      <c r="N11" s="3">
+      <c r="M11" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="N11" s="3" t="n">
         <v>0.25</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -5621,78 +5616,78 @@
           <t>none</t>
         </is>
       </c>
-      <c r="P11" s="3">
-        <v>0.0</v>
+      <c r="P11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q11" s="3" t="n"/>
       <c r="R11" s="3" t="n"/>
-      <c r="S11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="U11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="V11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="X11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AA11" s="3">
+      <c r="S11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AB11" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AC11" s="3" t="n">
         <v>2.744</v>
       </c>
-      <c r="AD11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AE11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AF11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AG11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AH11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AI11" s="3">
-        <v>0.0</v>
+      <c r="AD11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
           <t>lf</t>
         </is>
       </c>
-      <c r="AK11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AL11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AM11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AN11" s="3">
-        <v>0.0</v>
+      <c r="AK11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n"/>
       <c r="AP11" s="3" t="n"/>
@@ -7137,8 +7132,8 @@
           <t>Max Depth:</t>
         </is>
       </c>
-      <c r="B2" s="3">
-        <v>-10.0</v>
+      <c r="B2" s="3" t="n">
+        <v>-10</v>
       </c>
       <c r="D2" s="24" t="inlineStr">
         <is>
@@ -7242,7 +7237,7 @@
           <t>Mat ID:</t>
         </is>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="56" t="inlineStr">
@@ -7712,11 +7707,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0.0</v>
+      <c r="A9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
@@ -7756,11 +7751,11 @@
       <c r="AR9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="B10" s="3">
-        <v>0.0</v>
+      <c r="A10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
@@ -7800,11 +7795,11 @@
       <c r="AR10" s="19" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="B11" s="3">
-        <v>10.0</v>
+      <c r="A11" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
@@ -7844,11 +7839,11 @@
       <c r="AR11" s="19" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3">
-        <v>35.0</v>
-      </c>
-      <c r="B12" s="3">
-        <v>10.0</v>
+      <c r="A12" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
@@ -10545,22 +10540,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3">
+      <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
-        <v>17.0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>16.0</v>
+      <c r="B3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Depth</t>
         </is>
       </c>
-      <c r="E3" s="3">
-        <v>-2.0</v>
+      <c r="E3" s="3" t="n">
+        <v>-2</v>
       </c>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
@@ -10665,7 +10660,6 @@
           <t>Entry X min:</t>
         </is>
       </c>
-      <c r="K8"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -10683,7 +10677,6 @@
           <t>Entry X max:</t>
         </is>
       </c>
-      <c r="K9"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -10701,7 +10694,6 @@
           <t>Exit X min:</t>
         </is>
       </c>
-      <c r="K10"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -10719,7 +10711,6 @@
           <t>Exit X max:</t>
         </is>
       </c>
-      <c r="K11"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -10737,7 +10728,6 @@
           <t>Center box X min:</t>
         </is>
       </c>
-      <c r="K12"/>
     </row>
     <row r="13">
       <c r="J13" s="14" t="inlineStr">
@@ -10745,7 +10735,6 @@
           <t>Center box X max:</t>
         </is>
       </c>
-      <c r="K13"/>
     </row>
     <row r="14">
       <c r="J14" s="14" t="inlineStr">
@@ -10753,7 +10742,6 @@
           <t>Center box Y min:</t>
         </is>
       </c>
-      <c r="K14"/>
     </row>
     <row r="15">
       <c r="J15" s="14" t="inlineStr">
@@ -10761,7 +10749,6 @@
           <t>Center box Y max:</t>
         </is>
       </c>
-      <c r="K15"/>
     </row>
     <row r="16">
       <c r="J16" s="14" t="inlineStr">
@@ -10769,7 +10756,7 @@
           <t>Max tangent depth:</t>
         </is>
       </c>
-      <c r="K16" s="52"/>
+      <c r="K16" s="52" t="n"/>
       <c r="L16" s="52" t="n"/>
       <c r="M16" s="52" t="n"/>
       <c r="N16" s="52" t="n"/>
@@ -10780,7 +10767,6 @@
           <t>Min slip depth:</t>
         </is>
       </c>
-      <c r="K17"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3:E42">
